--- a/output/pdf_financials_xlsx/ROVA.xlsx
+++ b/output/pdf_financials_xlsx/ROVA.xlsx
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009486</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000285</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.306407</v>
+        <v>-6.296921</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.02269</v>
+        <v>-5.022405</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.277086</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.306407</v>
+        <v>-6.296921</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.018864</v>
+        <v>-5.018579</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.27401</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROVA.xlsx
+++ b/output/pdf_financials_xlsx/ROVA.xlsx
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.611053</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.178012</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.536139</v>
       </c>
     </row>
     <row r="65">
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.421681</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.243651</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.034148</v>
       </c>
     </row>
     <row r="68">
